--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -450,111 +450,111 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 本文件控制分类总表与 B_std 中「一级/二级」下拉选项。</t>
+          <t>【分类粒度原则 — 必须遵守】</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. 改完保存后执行：</t>
+          <t xml:space="preserve">  ✓ 只设业务大类：如 混凝土、钢筋、砖及砌块、泵车租赁、银行手续费</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">     python 财务付款一体化.py import-taxonomy</t>
+          <t xml:space="preserve">  ✗ 不要设型号/规格/强度：如 C25/C30、HRB400、350×350、Q355B、某品牌型号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   会写回 learn_classify/data/taxonomy.json，并可用于刷新下拉。</t>
+          <t xml:space="preserve">  摘要里出现「C30混凝土」→ 仍归「混凝土」，不新建「C30」类。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3. 导出最新体系：</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">     python 财务付款一体化.py export-taxonomy</t>
+          <t>1. 本文件控制分类总表与 B_std 中「一级/二级」下拉选项。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2. 改完保存后执行：</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【一级科目】表</t>
+          <t xml:space="preserve">     python 财务付款一体化.py import-taxonomy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ID：稳定标识，尽量不要改（改了需做 migrate 迁移旧记忆）</t>
+          <t xml:space="preserve">   会写回 learn_classify/data/taxonomy.json，并可用于刷新下拉。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 名称：界面显示名，可改</t>
+          <t>3. 导出最新体系：</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 排序：数字越小越靠前</t>
+          <t xml:space="preserve">     python 财务付款一体化.py export-taxonomy</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 启用：是/否（否=下拉中隐藏，旧数据仍可保留）</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【一级科目】表</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【二级科目】表</t>
+          <t xml:space="preserve">  - ID：稳定标识，尽量不要改（改了需做 migrate 迁移旧记忆）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 所属一级名称：必填，须与一级表「名称」一致（或填所属一级ID）</t>
+          <t xml:space="preserve">  - 名称：界面显示名，可改</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 新增二级：ID 可留空，导入时自动生成</t>
+          <t xml:space="preserve">  - 排序：数字越小越靠前</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 别名：多个用英文分号 ; 分隔</t>
+          <t xml:space="preserve">  - 启用：是/否（否=下拉中隐藏，旧数据仍可保留）</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>当前版本: 1.1.0</t>
+          <t>【二级科目】表</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 所属一级名称：必填，须与一级表「名称」一致（或填所属一级ID）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 新增二级：ID 可留空，导入时自动生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 别名：同义词/俗称（实心砖、商混），不要写强度等级或型号</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>当前版本: 1.2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>待复核二级ID: L2_pending</t>
         </is>
@@ -1017,7 +1048,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C25;C30;C35;商品混凝土;商混;砼</t>
+          <t>商品混凝土;商混;砼</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1085,7 +1116,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>待分类;(空白)</t>
+          <t>(空白);待分类</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2025,7 +2056,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>手续费;银行转账手续费;转账手续费;电汇费</t>
+          <t>手续费;电汇费;转账手续费;银行转账手续费</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2124,11 +2155,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「材料采购」</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2161,7 +2196,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>铲车;装载机;装载机租赁</t>
+          <t>装载机;装载机租赁;铲车</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2263,7 +2298,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>取现;开工仪式;换汇</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>兜底类，规则低优先级</t>
@@ -2333,7 +2372,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>95汽油;B7;加油;加油费;柴油;汽油;燃油</t>
+          <t>95汽油;加油;加油费;柴油;汽油;燃油</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2405,7 +2444,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>园区水费;水费;现场用水;电费</t>
+          <t>园区水费;水费;现场用水;电费;饮用水付款</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2441,7 +2480,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>带关费;保关费;报关;清关</t>
+          <t>保关费;带关费;报关;清关</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2541,7 +2580,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BOI;DBD;回头签;工作签;工签;签证;落地签</t>
+          <t>BOI;DBD;回头签;工作签;工签;签证;签证费;落地签</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2608,11 +2647,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「差旅费」</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2640,11 +2683,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「水电费」</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2672,11 +2719,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2704,11 +2755,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「办公费」</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2736,11 +2791,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2805,7 +2864,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>实心砖;空心砖;加气块;砌块;水泥砖</t>
+          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2877,7 +2936,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>水泥;砂浆;抹灰砂浆;砌筑砂浆;预拌砂浆</t>
+          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2908,11 +2967,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2945,7 +3008,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>河沙;机制砂;黄沙;沙子;中砂;粗砂</t>
+          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -2976,11 +3039,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3013,7 +3080,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>模板;木方;木模板;胶合板</t>
+          <t>木方;木模板;模板;胶合板</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -3044,11 +3111,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3081,7 +3152,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>苏博特;减水剂;外加剂</t>
+          <t>减水剂;外加剂;苏博特</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3193,7 +3264,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>网费;网络费;宽带;电话费;通讯费</t>
+          <t>宽带;电话费;网络费;网费;通讯费</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3224,11 +3295,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3261,7 +3336,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>五金;hardware;DOHOME;HARDWAREHOUSE;零星材料;辅材</t>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3292,11 +3367,15 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「投标保证金」</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3329,7 +3408,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>邮寄费;邮寄费用;快递费;快递</t>
+          <t>快递;快递费;邮寄费;邮寄费用</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3401,7 +3480,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>保险;保费;车辆保险;工程保险</t>
+          <t>保费;保险;工程保险;车辆保险</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3437,7 +3516,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>图纸;设计费;转图;图纸签字;工程师签字</t>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3509,7 +3588,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>劳保;安全帽;手套;反光背心;安全带;工作服</t>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3545,7 +3624,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>煤气;燃气;厨房煤气;食堂煤气;液化气;煤气费用</t>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3621,7 +3700,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>治安管理;治安管理费;治安管理付款</t>
+          <t>治安管理;治安管理付款;治安管理费</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3657,7 +3736,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>施工许可;劳工部检查;签字费</t>
+          <t>劳工部检查;施工许可;签字费</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3693,7 +3772,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;车辆维修;设备维修;补胎</t>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3729,7 +3808,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>差旅;机票;机票款;酒店</t>
+          <t>差旅;机票;机票款;酒店;飞签</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3807,7 +3886,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>履约保证金</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>seed extra</t>
@@ -3837,7 +3920,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
     </row>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -10,11 +10,13 @@
     <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="一级科目" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="二级科目" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="_meta" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="三级科目" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="_meta" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -440,7 +442,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>【一级/二级科目体系】编辑说明</t>
+          <t>【科目体系 · 三级分类】</t>
         </is>
       </c>
     </row>
@@ -450,28 +452,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【分类粒度原则 — 必须遵守】</t>
+          <t>结构：一级 → 二级 → 三级（可选）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓ 只设业务大类：如 混凝土、钢筋、砖及砌块、泵车租赁、银行手续费</t>
+          <t xml:space="preserve">  例：6_管理费 → 办公费 → 网络通讯费 / 邮寄快递费 / 办公物品采购 / 其他办公</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✗ 不要设型号/规格/强度：如 C25/C30、HRB400、350×350、Q355B、某品牌型号</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  摘要里出现「C30混凝土」→ 仍归「混凝土」，不新建「C30」类。</t>
+          <t>粒度：业务大类，不要型号规格（C30/HRB400 等）。</t>
         </is>
       </c>
     </row>
@@ -481,126 +479,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. 本文件控制分类总表与 B_std 中「一级/二级」下拉选项。</t>
+          <t>1. 改完保存后：python 财务付款一体化.py import-taxonomy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2. 改完保存后执行：</t>
+          <t>2. 导出：python 财务付款一体化.py export-taxonomy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">     python 财务付款一体化.py import-taxonomy</t>
+          <t>3. 刷新总表下拉：python 财务付款一体化.py export-class</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   会写回 learn_classify/data/taxonomy.json，并可用于刷新下拉。</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3. 导出最新体系：</t>
+          <t>【一级】ID / 名称 / 排序 / 启用 / 备注</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">     python 财务付款一体化.py export-taxonomy</t>
+          <t>【二级】所属一级名称或ID；别名用分号分隔</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【三级】所属二级名称或ID；无三级的二级可不建三级</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>【一级科目】表</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ID：稳定标识，尽量不要改（改了需做 migrate 迁移旧记忆）</t>
+          <t>当前版本: 2.0.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 名称：界面显示名，可改</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 排序：数字越小越靠前</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 启用：是/否（否=下拉中隐藏，旧数据仍可保留）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>【二级科目】表</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 所属一级名称：必填，须与一级表「名称」一致（或填所属一级ID）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 新增二级：ID 可留空，导入时自动生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 别名：同义词/俗称（实心砖、商混），不要写强度等级或型号</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>当前版本: 1.2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
         <is>
           <t>待复核二级ID: L2_pending</t>
         </is>
@@ -834,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1624,10 +1556,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>办公用品;生活用品;行政用品;行政采购</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>办公用品;办公费;生活用品;行政用品;行政采购</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3236,12 +3172,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2_mgmt_net</t>
+          <t>L2_mgmt_toll</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>网络通讯费</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3259,71 +3195,71 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>宽带;电话费;网络费;网费;通讯费</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2_mgmt_toll</t>
+          <t>L2_mat_hardware</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>五金辅材</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2_mat_hardware</t>
+          <t>L2_mgmt_perf_bond</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>五金辅材</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3331,25 +3267,25 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「投标保证金」</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2_mgmt_perf_bond</t>
+          <t>L2_mgmt_fuel2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>燃料动力</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3363,7 +3299,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3373,19 +3309,19 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「投标保证金」</t>
+          <t>停用：合并到燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2_mgmt_post</t>
+          <t>L2_mgmt_insurance</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>邮寄快递费</t>
+          <t>保险费</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3399,7 +3335,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3408,7 +3344,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>快递;快递费;邮寄费;邮寄费用</t>
+          <t>保费;保险;工程保险;车辆保险</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3416,12 +3352,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel2</t>
+          <t>L2_mgmt_design</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>燃料动力</t>
+          <t>图纸设计费</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3435,29 +3371,29 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>停用：合并到燃料及动力</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2_mgmt_insurance</t>
+          <t>L2_mgmt_fuel3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>保险费</t>
+          <t>燃料</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3471,29 +3407,29 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>保费;保险;工程保险;车辆保险</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>停用：合并到燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2_mgmt_design</t>
+          <t>L2_mgmt_ppe</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>图纸设计费</t>
+          <t>劳保用品</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3507,7 +3443,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3516,7 +3452,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3524,12 +3460,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel3</t>
+          <t>L2_mgmt_gas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>燃气煤气费</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3543,29 +3479,33 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>停用：合并到燃料及动力</t>
+          <t>食堂/宿舍燃气；加油归燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2_mgmt_ppe</t>
+          <t>L2_mgmt_reimburse</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>劳保用品</t>
+          <t>费用报销</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3579,7 +3519,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3588,7 +3528,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
+          <t>报销;日常费用;郝阳报销</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3596,12 +3536,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2_mgmt_gas</t>
+          <t>L2_mgmt_police</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>燃气煤气费</t>
+          <t>治安管理费</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3615,7 +3555,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3624,24 +3564,20 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>食堂/宿舍燃气；加油归燃料及动力</t>
-        </is>
-      </c>
+          <t>治安管理;治安管理付款;治安管理费</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2_mgmt_reimburse</t>
+          <t>L2_mgmt_permit_sign</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>费用报销</t>
+          <t>施工许可签字费</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3655,7 +3591,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3664,7 +3600,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>报销;日常费用;郝阳报销</t>
+          <t>劳工部检查;施工许可;签字费</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3672,26 +3608,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_eq_repair</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>机具维修</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3700,7 +3636,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>治安管理;治安管理付款;治安管理费</t>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3708,12 +3644,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_travel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>差旅费</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3727,7 +3663,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3736,34 +3672,38 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>劳工部检查;施工许可;签字费</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>差旅;机票;机票款;酒店;飞签</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_mgmt_tax</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>税款</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3772,20 +3712,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>WHT;增值税;补缴税;预扣税</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel</t>
+          <t>L2_mgmt_bid_bond</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>差旅费</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3799,7 +3743,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3808,7 +3752,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>差旅;机票;机票款;酒店;飞签</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3817,88 +3761,8 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>L2_mgmt_tax</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>税款</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>L1_mgmt</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>6_管理费</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>81</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>WHT;增值税;补缴税;预扣税</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>L2_mgmt_bid_bond</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>投标保证金</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>L1_mgmt</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>6_管理费</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>82</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>履约保证金</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H87"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3909,6 +3773,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>所属二级ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>所属二级名称</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>启用</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L3_office_net</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>网络通讯费</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L2_mgmt_office</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>办公费</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>宽带;电话费;网络;网络费;网费;通讯费</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>由原二级迁入办公费三级</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L3_office_post</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>邮寄快递费</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L2_mgmt_office</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>办公费</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>快递;快递费;邮寄费;邮寄费用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>由原二级迁入办公费三级</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L3_office_supplies</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>办公物品采购</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>L2_mgmt_office</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>办公费</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>办公用品;行政采购;行政用品;文具;打印耗材;硒鼓;纸张</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>办公费三级</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L3_office_other</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>其他办公</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L2_mgmt_office</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>办公费</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>生活用品</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>办公费兜底三级</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3920,7 +4011,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1.2.0</t>
+          <t>2.0.0</t>
         </is>
       </c>
     </row>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="一级科目" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="二级科目" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="三级科目" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="_meta" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一级科目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="二级科目" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三级科目" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>当前版本: 2.0.0</t>
+          <t>当前版本: 2.2.0</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -754,8 +754,58 @@
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L1_tax</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7_税金</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>70</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>印花税、预扣税、增值税等税款（不进管理费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L1_deposit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8_押金保证金</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>押金、投标/履约保证金等（独立大类）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -766,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1014,7 +1064,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>招待;宴请;客户餐;业务招待</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1254,7 +1308,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>关税;物流费;关税物流;进口税</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1288,7 +1346,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>圆钢;型钢;工字钢;槽钢;盘圆;线材;螺纹钢;角钢;钢板;钢绞线</t>
+          <t>圆钢;型钢;工字钢;槽钢;盘圆;线材;螺纹钢;角钢;钢绞线</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1324,7 +1382,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>体检;医疗;治安;药品</t>
+          <t>体检;医疗;药品;安全费;安全文明</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1556,7 +1614,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>办公用品;办公费;生活用品;行政用品;行政采购</t>
+          <t>办公费;行政办公</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1710,12 +1768,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1726,7 +1784,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>借支;备用金;预支</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1892,7 +1954,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>危废;危废处理;垃圾处理;建筑垃圾;清运</t>
+          <t>危废;危废处理;垃圾处理;建筑垃圾;清运;垃圾清理;垃圾清理费;场地清理;渣土</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2028,10 +2090,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ETC;皮卡;租车;车辆租赁;过路费</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>ETC;皮卡;租车;车辆租赁;过路费;过路过桥;车辆使用</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>车辆租赁/过路等；车辆用油单独</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2170,7 +2236,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2236,12 +2306,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>取现;开工仪式;换汇</t>
+          <t>取现;换汇</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>兜底类，规则低优先级</t>
+          <t>兜底；安保费已独立</t>
         </is>
       </c>
     </row>
@@ -2308,10 +2378,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>95汽油;加油;加油费;柴油;汽油;燃油</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>燃油;加油;加油费;柴油</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>无法区分机具/车辆用油时的兜底</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2380,30 +2454,34 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>园区水费;水费;现场用水;电费;饮用水付款</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>水电;水电费合计</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L2_log_customs_agent</t>
+          <t>L2_dep_deposit</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>报关带关费</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2416,7 +2494,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>保关费;带关费;报关;清关</t>
+          <t>押金;保证金退还;押金退还</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2424,22 +2502,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L2_mgmt_deposit</t>
+          <t>L2_log_customs_agent</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>报关带关费</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2450,18 +2528,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L2_mgmt_park</t>
+          <t>L2_mgmt_deposit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>园区管理费</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2475,25 +2557,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>押金;保证金退还</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit</t>
+          <t>L2_mgmt_park</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>证件许可</t>
+          <t>园区管理费</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2507,29 +2597,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>BOI;DBD;回头签;工作签;工签;签证;签证费;落地签</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L2_mgmt_rent</t>
+          <t>L2_mgmt_permit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>房租物业费</t>
+          <t>证件许可</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2543,7 +2629,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2552,20 +2638,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>宿舍;宿舍租金;房租;营地</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>BOI;DBD;证件;证件许可;许可证;劳工证</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>工作签/施工许可类证件；商务签证归签证费用</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L2_mgmt_flyvisa</t>
+          <t>L2_mgmt_rent</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>飞签</t>
+          <t>房租物业费</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2579,29 +2669,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「差旅费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2_mgmt_water</t>
+          <t>L2_mgmt_flyvisa</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>饮用水付款</t>
+          <t>飞签</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2615,7 +2705,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2625,55 +2715,59 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「水电费」</t>
+          <t xml:space="preserve"> | 并入大类「差旅费」</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L2_mgmt_workvisa</t>
+          <t>L2_mat_plate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>工作签</t>
+          <t>钢板</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+          <t>钢板费用，不归钢筋</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L2_mgmt_admin</t>
+          <t>L2_mgmt_water</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>行政用品</t>
+          <t>饮用水付款</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2687,7 +2781,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2697,19 +2791,19 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「办公费」</t>
+          <t xml:space="preserve"> | 并入大类「水电费」</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L2_mgmt_ceremony</t>
+          <t>L2_mgmt_workvisa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>开工仪式</t>
+          <t>工作签</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2723,7 +2817,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2733,19 +2827,19 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2_mgmt_stamp</t>
+          <t>L2_mgmt_admin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>印花税</t>
+          <t>行政用品</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2759,39 +2853,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「办公费」</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L2_mat_brick</t>
+          <t>L2_mgmt_ceremony</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>砖及砌块</t>
+          <t>奠基仪式费用</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2800,70 +2898,74 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
+          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>数据优化</t>
+          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L2_mgmt_agency</t>
+          <t>L2_mgmt_stamp</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中介费</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_tax</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>7_税金</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>印花税</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L2_mat_cement</t>
+          <t>L2_dep_bid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>水泥及砂浆</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2872,7 +2974,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
+          <t>投标保证金;投标保证</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2880,84 +2982,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L2_mgmt_cash</t>
+          <t>L2_mat_brick</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>取现</t>
+          <t>砖及砌块</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t>数据优化</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L2_mat_sand</t>
+          <t>L2_mgmt_agency</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>砂</t>
+          <t>中介费</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L2_mgmt_fx</t>
+          <t>L2_mgmt_visa_fee</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>换汇</t>
+          <t>签证费用</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2971,29 +3073,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;落地签;转签;飞签</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t>出入境签证；工作签归证件许可</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L2_mat_formwork</t>
+          <t>L2_mat_cement</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>模板木方</t>
+          <t>水泥及砂浆</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3007,7 +3113,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3016,7 +3122,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>木方;木模板;模板;胶合板</t>
+          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -3024,12 +3130,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa</t>
+          <t>L2_mgmt_cash</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>签证费</t>
+          <t>取现</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3043,7 +3149,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3053,33 +3159,33 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L2_mat_admix</t>
+          <t>L2_mgmt_work_visa</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>外加剂</t>
+          <t>工作签证费用</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3088,34 +3194,38 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>减水剂;外加剂;苏博特</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>工作签;工签;工作签证;工作签费用;临时工作签;工作签费;工签费</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>工作签证相关；与商务签证、证件许可区分</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L2_mgmt_test</t>
+          <t>L2_mat_sand</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>检验试验费</t>
+          <t>砂</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3124,168 +3234,164 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>替换/细化原检验试验</t>
-        </is>
-      </c>
+          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L2_mat_slag</t>
+          <t>L2_mgmt_fx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>炉渣灰渣</t>
+          <t>换汇</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>炉渣;炉渣款;粉煤灰</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2_mgmt_toll</t>
+          <t>L2_mat_formwork</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>模板木方</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>木方;木模板;模板;胶合板</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2_mat_hardware</t>
+          <t>L2_mgmt_visa</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>五金辅材</t>
+          <t>签证费</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2_mgmt_perf_bond</t>
+          <t>L2_mat_admix</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>外加剂</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「投标保证金」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>减水剂;外加剂;苏博特</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel2</t>
+          <t>L2_mgmt_test</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>燃料动力</t>
+          <t>检验试验费</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3299,43 +3405,47 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>停用：合并到燃料及动力</t>
+          <t>替换/细化原检验试验</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2_mgmt_insurance</t>
+          <t>L2_mat_slag</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>保险费</t>
+          <t>炉渣灰渣</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3344,7 +3454,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>保费;保险;工程保险;车辆保险</t>
+          <t>炉渣;炉渣款;粉煤灰</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3352,12 +3462,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2_mgmt_design</t>
+          <t>L2_mgmt_toll</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>图纸设计费</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3371,65 +3481,65 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel3</t>
+          <t>L2_mat_hardware</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>五金辅材</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>停用：合并到燃料及动力</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2_mgmt_ppe</t>
+          <t>L2_mgmt_perf_bond</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>劳保用品</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3443,29 +3553,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2_mgmt_gas</t>
+          <t>L2_mgmt_fuel2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>燃气煤气费</t>
+          <t>燃料动力</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3479,33 +3589,29 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>食堂/宿舍燃气；加油归燃料及动力</t>
+          <t>停用：合并到燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2_mgmt_reimburse</t>
+          <t>L2_mgmt_insurance</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>费用报销</t>
+          <t>保险费</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3519,7 +3625,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3528,7 +3634,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>报销;日常费用;郝阳报销</t>
+          <t>保费;保险;工程保险;车辆保险</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3536,12 +3642,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_mgmt_design</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>图纸设计费</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3555,7 +3661,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3564,7 +3670,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>治安管理;治安管理付款;治安管理费</t>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3572,12 +3678,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_fuel3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>燃料</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3591,43 +3697,43 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>劳工部检查;施工许可;签字费</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>停用：合并到燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_mgmt_ppe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>劳保用品</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3636,7 +3742,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3644,26 +3750,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel</t>
+          <t>L2_dep_perf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>差旅费</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3672,24 +3778,20 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>差旅;机票;机票款;酒店;飞签</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
+          <t>履约保证金;履约保证</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2_mgmt_tax</t>
+          <t>L2_mgmt_gas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>税款</t>
+          <t>燃气煤气费</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3703,7 +3805,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3712,57 +3814,817 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>WHT;增值税;补缴税;预扣税</t>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>食堂/宿舍燃气；加油归燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>L2_mgmt_water_fee</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>水费</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>30</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>施工/园区/工业用水；不含桶装饮用水</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L2_mgmt_elec_fee</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>电费</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>31</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>施工/临时用电；不含燃料发电</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L2_mgmt_reimburse</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>费用报销</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>31</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>报销;日常费用;郝阳报销</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L2_mgmt_drink_water</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>现场饮用水</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>32</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>现场/办公室饮用桶装水等</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L2_mgmt_police</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>治安管理费</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>32</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>治安管理;治安管理付款;治安管理费</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L2_mgmt_permit_sign</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>施工许可签字费</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>33</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>劳工部检查;施工许可;签字费</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L2_eq_repair</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>机具维修</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>L1_equip</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3_机具费</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>40</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L2_exclude_agent_pay</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>代付款</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>L1_exclude</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>不计入成本</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>40</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>代付/代xx付款，不计入管理费与成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L2_mgmt_fuel_equip</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>机具发电用油</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>40</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>施工机具、发电机用柴油等</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L2_mgmt_fuel_vehicle</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>车辆用油</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>41</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>交通车辆用油</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>L2_mgmt_airfare</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>机票费</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>机票;机票款;航空票;机票费用</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>L2_mgmt_transit</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>交通费</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>51</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>市内/城际交通，不含车辆租赁与过路</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L2_mgmt_travel_allow</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>出差补助</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>52</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>L2_mgmt_security_fee</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>安保费</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>60</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>安保;安保费用;保安费;门岗;门卫费</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>非工资类安保服务费；保安工资在人工费</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L2_mat_floor</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>地坪硬化</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>80</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L2_mgmt_travel</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>80</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>差旅;差旅费;酒店;住宿;宾馆</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>差旅综合；机票/交通/补助请用细分科目</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L2_mat_gate</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>门楼</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>81</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>大门;门楼施工;门头</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L2_mgmt_tax</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>税款</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>L1_tax</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>7_税金</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>81</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_build</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>现场临建用房</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>82</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>L2_mgmt_bid_bond</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>投标保证金</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>L1_mgmt</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>6_管理费</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E104" t="n">
         <v>82</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>履约保证金</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_fence</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>现场临时围墙</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>83</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:H105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4011,7 +4873,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>2.2.0</t>
         </is>
       </c>
     </row>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>当前版本: 2.2.0</t>
+          <t>当前版本: 2.5.0</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>圆钢;型钢;工字钢;槽钢;盘圆;线材;螺纹钢;角钢;钢绞线</t>
+          <t>圆钢;盘圆;线材;螺纹钢;钢筋;钢绞线</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1377,15 +1377,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>体检;医疗;药品;安全费;安全文明</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 已并入治安管理费；体检/医疗→医务费用</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1454,22 +1454,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L2_exclude_other</t>
+          <t>L2_exclude_agent_pay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>代付款</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_sub</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>0_分包</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1480,32 +1480,36 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>代付/代垫款；归属 0_分包（计入成本）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L2_labor_mm</t>
+          <t>L2_exclude_other</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>缅工</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1517,27 +1521,31 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L2_lease_pipe</t>
+          <t>L2_labor_mm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>钢管租赁</t>
+          <t>缅工</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1554,22 +1562,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L2_mat_pile</t>
+          <t>L2_lease_pipe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>桩</t>
+          <t>钢管租赁</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1586,22 +1594,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L2_mgmt_office</t>
+          <t>L2_mat_pile</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>办公费</t>
+          <t>桩</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1612,68 +1620,68 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>办公费;行政办公</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L2_eq_crane</t>
+          <t>L2_mgmt_office</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>吊车租赁</t>
+          <t>办公费</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>中央空调安装;分体空调;办公空调;办公费;安装空调;空调;空调安装;空调移机;空调维修;空调费;行政办公</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L2_labor_local</t>
+          <t>L2_eq_crane</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>属地员工</t>
+          <t>吊车租赁</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1690,22 +1698,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L2_lease_container</t>
+          <t>L2_labor_local</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>集装箱租赁</t>
+          <t>属地员工</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1918,7 +1926,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>施工物资;材料报销;材料费;材料采购付款;材料采购费用;物资采购</t>
+          <t>C型钢;H型钢;型钢;工字钢;扁钢;方钢;施工物资;材料报销;材料费;材料采购付款;材料采购费用;槽钢;物资采购;角钢;钢结构件;预埋;预埋件;预埋钢板</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2638,7 +2646,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BOI;DBD;证件;证件许可;许可证;劳工证</t>
+          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3082,7 +3090,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;落地签;转签;飞签</t>
+          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>工作签;工签;工作签证;工作签费用;临时工作签;工作签费;工签费</t>
+          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3982,12 +3990,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_mgmt_permit_sign</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>施工许可签字费</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4001,7 +4009,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4010,7 +4018,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>治安管理;治安管理付款;治安管理费</t>
+          <t>劳工部检查;施工许可;签字费</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4018,12 +4026,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_police</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>治安管理费</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4037,7 +4045,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4046,34 +4054,38 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>劳工部检查;施工许可;签字费</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_mgmt_medical</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>医务费用</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4082,30 +4094,34 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>各项医务、体检、医疗费用</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L2_exclude_agent_pay</t>
+          <t>L2_eq_repair</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>代付款</t>
+          <t>机具维修</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4118,14 +4134,10 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>代付/代xx付款，不计入管理费与成本</t>
-        </is>
-      </c>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4345,17 +4357,13 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>安保;安保费用;保安费;门岗;门卫费</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>非工资类安保服务费；保安工资在人工费</t>
+          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
         </is>
       </c>
     </row>
@@ -4514,22 +4522,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L2_mat_temp_build</t>
+          <t>L2_mgmt_bid_bond</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>现场临建用房</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -4537,25 +4545,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>履约保证金</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L2_mgmt_bid_bond</t>
+          <t>L2_mat_temp_build</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>现场临建用房</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4569,21 +4581,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>现场临建用房/活动板房等；归属 6_管理费</t>
         </is>
       </c>
     </row>
@@ -4600,16 +4612,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4621,10 +4633,50 @@
           <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>现场临时围墙/围挡；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L2_lease_container</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>集装箱租赁</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>92</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>集装箱租赁（非集装箱房临建）；归属 6_管理费</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H105"/>
+  <autoFilter ref="A1:H106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4873,7 +4925,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.2.0</t>
+          <t>2.5.0</t>
         </is>
       </c>
     </row>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>当前版本: 2.5.0</t>
+          <t>当前版本: 2.5.0+auto</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4522,22 +4522,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L2_mgmt_bid_bond</t>
+          <t>L2_auto_混凝土及泵车</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>混凝土及泵车</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -4545,29 +4545,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>履约保证金</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>auto from learn_pool</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L2_mat_temp_build</t>
+          <t>L2_mgmt_bid_bond</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>现场临建用房</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4581,33 +4577,33 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L2_mat_temp_fence</t>
+          <t>L2_mat_temp_build</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>现场临时围墙</t>
+          <t>现场临建用房</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4621,7 +4617,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4630,53 +4626,93 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>现场临时围墙/围挡；归属 6_管理费</t>
+          <t>现场临建用房/活动板房等；归属 6_管理费</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>L2_mat_temp_fence</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>现场临时围墙</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>91</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>现场临时围墙/围挡；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>L2_lease_container</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>集装箱租赁</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>L1_mgmt</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>6_管理费</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
         <v>92</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
         <is>
           <t>集装箱租赁（非集装箱房临建）；归属 6_管理费</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H106"/>
+  <autoFilter ref="A1:H107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4925,7 +4961,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.5.0</t>
+          <t>2.5.0+auto</t>
         </is>
       </c>
     </row>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2178,22 +2178,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L2_eq_loader</t>
+          <t>L2_auto_缅工营地</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>铲车租赁</t>
+          <t>缅工营地</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2204,36 +2204,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>装载机;装载机租赁;铲车</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>含装载机</t>
+          <t>auto from learn_pool</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L2_mgmt_food</t>
+          <t>L2_eq_loader</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>伙食费</t>
+          <t>铲车租赁</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2246,62 +2242,70 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>装载机;装载机租赁;铲车</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>含装载机</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L2_eq_boom</t>
+          <t>L2_mgmt_food</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>曲臂车租赁</t>
+          <t>伙食费</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L2_mgmt_other</t>
+          <t>L2_eq_boom</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>曲臂车租赁</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2312,68 +2316,68 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>取现;换汇</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>兜底；安保费已独立</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L2_eq_flatbed</t>
+          <t>L2_mgmt_other</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>平板车租赁</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>取现;换汇</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>兜底；安保费已独立</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel</t>
+          <t>L2_eq_flatbed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>燃料及动力</t>
+          <t>平板车租赁</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2384,40 +2388,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>燃油;加油;加油费;柴油</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>无法区分机具/车辆用油时的兜底</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L2_eq_general</t>
+          <t>L2_mgmt_fuel</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>机具使用费</t>
+          <t>燃料及动力</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2426,30 +2422,34 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>燃油;加油;加油费;柴油</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>无法区分机具/车辆用油时的兜底</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L2_mgmt_util</t>
+          <t>L2_eq_general</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>水电费</t>
+          <t>机具使用费</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2462,38 +2462,34 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>水电;水电费合计</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
-        </is>
-      </c>
+          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L2_dep_deposit</t>
+          <t>L2_mgmt_util</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>水电费</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2502,30 +2498,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>押金;保证金退还;押金退还</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>水电;水电费合计</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L2_log_customs_agent</t>
+          <t>L2_dep_deposit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>报关带关费</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
+          <t>押金;保证金退还;押金退还</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2546,22 +2546,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L2_mgmt_deposit</t>
+          <t>L2_log_customs_agent</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>报关带关费</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2569,29 +2569,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>押金;保证金退还</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
-        </is>
-      </c>
+          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L2_mgmt_park</t>
+          <t>L2_mgmt_deposit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>园区管理费</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2605,25 +2601,33 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>押金;保证金退还</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit</t>
+          <t>L2_mgmt_park</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>证件许可</t>
+          <t>园区管理费</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2637,33 +2641,25 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>工作签/施工许可类证件；商务签证归签证费用</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L2_mgmt_rent</t>
+          <t>L2_mgmt_permit</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>房租物业费</t>
+          <t>证件许可</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2677,7 +2673,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2686,20 +2682,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>工作签/施工许可类证件；商务签证归签证费用</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2_mgmt_flyvisa</t>
+          <t>L2_mgmt_rent</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>飞签</t>
+          <t>房租物业费</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2713,79 +2713,75 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「差旅费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L2_mat_plate</t>
+          <t>L2_mgmt_flyvisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>钢板</t>
+          <t>飞签</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>钢板费用，不归钢筋</t>
+          <t xml:space="preserve"> | 并入大类「差旅费」</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L2_mgmt_water</t>
+          <t>L2_mat_plate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>饮用水付款</t>
+          <t>钢板</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2793,25 +2789,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「水电费」</t>
+          <t>钢板费用，不归钢筋</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L2_mgmt_workvisa</t>
+          <t>L2_mgmt_water</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>工作签</t>
+          <t>饮用水付款</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2835,19 +2835,19 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+          <t xml:space="preserve"> | 并入大类「水电费」</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2_mgmt_admin</t>
+          <t>L2_mgmt_workvisa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>行政用品</t>
+          <t>工作签</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2871,19 +2871,19 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「办公费」</t>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L2_mgmt_ceremony</t>
+          <t>L2_mgmt_admin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>奠基仪式费用</t>
+          <t>行政用品</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2897,47 +2897,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
+          <t xml:space="preserve"> | 并入大类「办公费」</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L2_mgmt_stamp</t>
+          <t>L2_mgmt_ceremony</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>印花税</t>
+          <t>奠基仪式费用</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2946,34 +2942,38 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>印花税</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L2_dep_bid</t>
+          <t>L2_mgmt_stamp</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_tax</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>7_税金</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>投标保证金;投标保证</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2990,22 +2990,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L2_mat_brick</t>
+          <t>L2_dep_bid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>砖及砌块</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3018,34 +3018,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>数据优化</t>
-        </is>
-      </c>
+          <t>投标保证金;投标保证</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L2_mgmt_agency</t>
+          <t>L2_mat_brick</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>中介费</t>
+          <t>砖及砌块</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3056,18 +3052,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>数据优化</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa_fee</t>
+          <t>L2_mgmt_agency</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>签证费用</t>
+          <t>中介费</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3088,40 +3092,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>出入境签证；工作签归证件许可</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L2_mat_cement</t>
+          <t>L2_mgmt_visa_fee</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>水泥及砂浆</t>
+          <t>签证费用</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3130,30 +3126,34 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>出入境签证；工作签归证件许可</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L2_mgmt_cash</t>
+          <t>L2_mat_cement</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>取现</t>
+          <t>水泥及砂浆</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3161,25 +3161,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L2_mgmt_work_visa</t>
+          <t>L2_mgmt_cash</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>工作签证费用</t>
+          <t>取现</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3197,43 +3197,39 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>工作签证相关；与商务签证、证件许可区分</t>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L2_mat_sand</t>
+          <t>L2_mgmt_work_visa</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>砂</t>
+          <t>工作签证费用</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3242,30 +3238,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>工作签证相关；与商务签证、证件许可区分</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L2_mgmt_fx</t>
+          <t>L2_mat_sand</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>换汇</t>
+          <t>砂</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3273,71 +3273,71 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2_mat_formwork</t>
+          <t>L2_mgmt_fx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>模板木方</t>
+          <t>换汇</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>木方;木模板;模板;胶合板</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa</t>
+          <t>L2_mat_formwork</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>签证费</t>
+          <t>模板木方</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3345,71 +3345,71 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>木方;木模板;模板;胶合板</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2_mat_admix</t>
+          <t>L2_mgmt_visa</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>外加剂</t>
+          <t>签证费</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>减水剂;外加剂;苏博特</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2_mgmt_test</t>
+          <t>L2_mat_admix</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>检验试验费</t>
+          <t>外加剂</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3422,38 +3422,34 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>替换/细化原检验试验</t>
-        </is>
-      </c>
+          <t>减水剂;外加剂;苏博特</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2_mat_slag</t>
+          <t>L2_mgmt_test</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>炉渣灰渣</t>
+          <t>检验试验费</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3462,30 +3458,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>炉渣;炉渣款;粉煤灰</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>替换/细化原检验试验</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2_mgmt_toll</t>
+          <t>L2_mat_slag</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>炉渣灰渣</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3493,71 +3493,71 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>炉渣;炉渣款;粉煤灰</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2_mat_hardware</t>
+          <t>L2_mgmt_toll</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>五金辅材</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2_mgmt_perf_bond</t>
+          <t>L2_mat_hardware</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>五金辅材</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -3565,25 +3565,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel2</t>
+          <t>L2_mgmt_perf_bond</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>燃料动力</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3607,19 +3607,19 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>停用：合并到燃料及动力</t>
+          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2_mgmt_insurance</t>
+          <t>L2_mgmt_fuel2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>保险费</t>
+          <t>燃料动力</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3637,25 +3637,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>保费;保险;工程保险;车辆保险</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>停用：合并到燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2_mgmt_design</t>
+          <t>L2_mgmt_insurance</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>图纸设计费</t>
+          <t>保险费</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
+          <t>保费;保险;工程保险;车辆保险</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3686,12 +3686,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel3</t>
+          <t>L2_mgmt_design</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>图纸设计费</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3709,25 +3709,25 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>停用：合并到燃料及动力</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2_mgmt_ppe</t>
+          <t>L2_mgmt_fuel3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>劳保用品</t>
+          <t>燃料</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3741,43 +3741,43 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>停用：合并到燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2_dep_perf</t>
+          <t>L2_mgmt_ppe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>劳保用品</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>履约保证金;履约保证</t>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3794,22 +3794,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2_mgmt_gas</t>
+          <t>L2_dep_perf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>燃气煤气费</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3822,24 +3822,20 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>食堂/宿舍燃气；加油归燃料及动力</t>
-        </is>
-      </c>
+          <t>履约保证金;履约保证</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L2_mgmt_water_fee</t>
+          <t>L2_mgmt_gas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>水费</t>
+          <t>燃气煤气费</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3862,24 +3858,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>施工/园区/工业用水；不含桶装饮用水</t>
+          <t>食堂/宿舍燃气；加油归燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L2_mgmt_elec_fee</t>
+          <t>L2_mgmt_water_fee</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>电费</t>
+          <t>水费</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3893,7 +3889,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3902,24 +3898,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
+          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>施工/临时用电；不含燃料发电</t>
+          <t>施工/园区/工业用水；不含桶装饮用水</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L2_mgmt_reimburse</t>
+          <t>L2_mgmt_elec_fee</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>费用报销</t>
+          <t>电费</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3942,20 +3938,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>报销;日常费用;郝阳报销</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>施工/临时用电；不含燃料发电</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L2_mgmt_drink_water</t>
+          <t>L2_mgmt_reimburse</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>现场饮用水</t>
+          <t>费用报销</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3978,24 +3978,20 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>现场/办公室饮用桶装水等</t>
-        </is>
-      </c>
+          <t>报销;日常费用;郝阳报销</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_drink_water</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>现场饮用水</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4009,7 +4005,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4018,20 +4014,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>劳工部检查;施工许可;签字费</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>现场/办公室饮用桶装水等</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_mgmt_permit_sign</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>施工许可签字费</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4054,24 +4054,20 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
-        </is>
-      </c>
+          <t>劳工部检查;施工许可;签字费</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2_mgmt_medical</t>
+          <t>L2_mgmt_police</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>医务费用</t>
+          <t>治安管理费</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4085,7 +4081,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4094,38 +4090,38 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
+          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>各项医务、体检、医疗费用</t>
+          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_mgmt_medical</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>医务费用</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4134,30 +4130,34 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>各项医务、体检、医疗费用</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_equip</t>
+          <t>L2_eq_repair</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>机具发电用油</t>
+          <t>机具维修</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -4170,24 +4170,20 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>施工机具、发电机用柴油等</t>
-        </is>
-      </c>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_vehicle</t>
+          <t>L2_mgmt_fuel_equip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>车辆用油</t>
+          <t>机具发电用油</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4201,7 +4197,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4210,24 +4206,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
+          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>交通车辆用油</t>
+          <t>施工机具、发电机用柴油等</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>L2_mgmt_airfare</t>
+          <t>L2_mgmt_fuel_vehicle</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>机票费</t>
+          <t>车辆用油</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4241,7 +4237,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4250,20 +4246,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>机票;机票款;航空票;机票费用</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>交通车辆用油</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L2_mgmt_transit</t>
+          <t>L2_mgmt_airfare</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>交通费</t>
+          <t>机票费</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4286,24 +4286,20 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>市内/城际交通，不含车辆租赁与过路</t>
-        </is>
-      </c>
+          <t>机票;机票款;航空票;机票费用</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel_allow</t>
+          <t>L2_mgmt_transit</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>出差补助</t>
+          <t>交通费</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4317,7 +4313,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4326,20 +4322,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>市内/城际交通，不含车辆租赁与过路</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L2_mgmt_security_fee</t>
+          <t>L2_mgmt_travel_allow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>安保费</t>
+          <t>出差补助</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4353,75 +4353,75 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L2_mat_floor</t>
+          <t>L2_mgmt_security_fee</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>地坪硬化</t>
+          <t>安保费</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel</t>
+          <t>L2_mat_floor</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>差旅费</t>
+          <t>地坪硬化</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4434,38 +4434,34 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>差旅;差旅费;酒店;住宿;宾馆</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>差旅综合；机票/交通/补助请用细分科目</t>
-        </is>
-      </c>
+          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L2_mat_gate</t>
+          <t>L2_mgmt_travel</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>门楼</t>
+          <t>差旅费</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4474,30 +4470,34 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>大门;门楼施工;门头</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>差旅;差旅费;酒店;住宿;宾馆</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>差旅综合；机票/交通/补助请用细分科目</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L2_mgmt_tax</t>
+          <t>L2_mat_gate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>税款</t>
+          <t>门楼</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -4510,70 +4510,70 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
+          <t>大门;门楼施工;门头</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L2_auto_混凝土及泵车</t>
+          <t>L2_mgmt_tax</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>混凝土及泵车</t>
+          <t>税款</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_tax</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>7_税金</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>auto from learn_pool</t>
+          <t>seed extra</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L2_mgmt_bid_bond</t>
+          <t>L2_auto_混凝土及泵车</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>混凝土及泵车</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -4581,29 +4581,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>履约保证金</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>auto from learn_pool</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L2_mat_temp_build</t>
+          <t>L2_mgmt_bid_bond</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>现场临建用房</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4617,33 +4613,33 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>L2_mat_temp_fence</t>
+          <t>L2_mat_temp_build</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>现场临时围墙</t>
+          <t>现场临建用房</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4657,7 +4653,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4666,53 +4662,93 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>现场临时围墙/围挡；归属 6_管理费</t>
+          <t>现场临建用房/活动板房等；归属 6_管理费</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>L2_mat_temp_fence</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>现场临时围墙</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>91</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>现场临时围墙/围挡；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>L2_lease_container</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>集装箱租赁</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>L1_mgmt</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>6_管理费</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
         <v>92</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
         <is>
           <t>集装箱租赁（非集装箱房临建）；归属 6_管理费</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H107"/>
+  <autoFilter ref="A1:H108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -804,8 +804,58 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L1_auto_工程款</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>工程款</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>81</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L1_auto_其他收款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>其他收款</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>82</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -816,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1146,22 +1196,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L2_eq_tower</t>
+          <t>L2_auto_业主付款</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>塔吊租赁</t>
+          <t>业主付款</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_auto_工程款</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1173,27 +1223,31 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L2_exclude_transfer</t>
+          <t>L2_auto_废旧物资处理</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>资金调拨</t>
+          <t>废旧物资处理</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_auto_其他收款</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>其他收款</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1207,29 +1261,29 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L2_labor_salary</t>
+          <t>L2_eq_tower</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>工资薪金</t>
+          <t>塔吊租赁</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1246,22 +1300,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L2_lease_plate</t>
+          <t>L2_exclude_transfer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>钢板租赁</t>
+          <t>资金调拨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1272,32 +1326,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TCB钢板;钢板租赁</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L2_log_customs</t>
+          <t>L2_labor_salary</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>关税物流费</t>
+          <t>工资薪金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1308,32 +1362,28 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>关税;物流费;关税物流;进口税</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L2_mat_steel</t>
+          <t>L2_lease_plate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>钢筋</t>
+          <t>钢板租赁</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1346,7 +1396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>圆钢;盘圆;线材;螺纹钢;钢筋;钢绞线</t>
+          <t>TCB钢板;钢板租赁</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1354,22 +1404,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L2_mgmt_safety</t>
+          <t>L2_log_customs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>安全费用</t>
+          <t>关税物流费</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1377,35 +1427,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 已并入治安管理费；体检/医疗→医务费用</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>关税;物流费;关税物流;进口税</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L2_sub_loan</t>
+          <t>L2_mat_steel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>分包借款</t>
+          <t>钢筋</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L1_sub</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0_分包</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1416,50 +1466,58 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>圆钢;盘圆;线材;螺纹钢;钢筋;钢绞线</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L2_eq_excavator</t>
+          <t>L2_mgmt_safety</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>挖机租赁</t>
+          <t>安全费用</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 已并入治安管理费；体检/医疗→医务费用</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L2_exclude_agent_pay</t>
+          <t>L2_sub_loan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>代付款</t>
+          <t>分包借款</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1473,43 +1531,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>代付/代垫款；归属 0_分包（计入成本）</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L2_exclude_other</t>
+          <t>L2_auto_地勘收款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>地勘收款</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_auto_其他收款</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>其他收款</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1523,29 +1573,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L2_labor_mm</t>
+          <t>L2_auto_进度款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>缅工</t>
+          <t>进度款</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_auto_工程款</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1557,27 +1607,31 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L2_lease_pipe</t>
+          <t>L2_eq_excavator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>钢管租赁</t>
+          <t>挖机租赁</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1594,22 +1648,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L2_mat_pile</t>
+          <t>L2_exclude_agent_pay</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>桩</t>
+          <t>代付款</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_sub</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>0_分包</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1620,28 +1674,36 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>代付/代垫款；归属 0_分包（计入成本）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L2_mgmt_office</t>
+          <t>L2_exclude_other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>办公费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1652,40 +1714,36 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>中央空调安装;分体空调;办公空调;办公费;安装空调;空调;空调安装;空调移机;空调维修;空调费;行政办公</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+          <t>seed extra</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L2_eq_crane</t>
+          <t>L2_labor_mm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>吊车租赁</t>
+          <t>缅工</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1698,26 +1756,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L2_labor_local</t>
+          <t>L2_lease_pipe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>属地员工</t>
+          <t>钢管租赁</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1730,12 +1788,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L2_mat_gravel</t>
+          <t>L2_mat_pile</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>碎石</t>
+          <t>桩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1749,43 +1807,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>寸石;石子;碎石料;级配砂石</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L2_mgmt_petty</t>
+          <t>L2_mgmt_office</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>备用金</t>
+          <t>办公费</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1794,34 +1848,38 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>借支;备用金;预支</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>中央空调安装;分体空调;办公空调;办公费;安装空调;空调;空调安装;空调移机;空调维修;空调费;行政办公</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L2_eq_truckcrane</t>
+          <t>L2_auto_工程款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>随车吊租赁</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_auto_工程款</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1829,31 +1887,35 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L2_labor_site</t>
+          <t>L2_eq_crane</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>工程劳工</t>
+          <t>吊车租赁</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1866,26 +1928,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L2_lease_form</t>
+          <t>L2_labor_local</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>钢膜租赁</t>
+          <t>属地员工</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1898,12 +1960,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L2_mat_generic</t>
+          <t>L2_mat_gravel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>材料采购</t>
+          <t>碎石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1917,7 +1979,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1926,7 +1988,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C型钢;H型钢;型钢;工字钢;扁钢;方钢;施工物资;材料报销;材料费;材料采购付款;材料采购费用;槽钢;物资采购;角钢;钢结构件;预埋;预埋件;预埋钢板</t>
+          <t>寸石;石子;碎石料;级配砂石</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1934,26 +1996,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L2_mgmt_clean</t>
+          <t>L2_mgmt_petty</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>场地清理费</t>
+          <t>备用金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1962,7 +2024,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>危废;危废处理;垃圾处理;建筑垃圾;清运;垃圾清理;垃圾清理费;场地清理;渣土</t>
+          <t>借支;备用金;预支</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1970,12 +2032,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L2_eq_generator</t>
+          <t>L2_eq_truckcrane</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>发电机租赁</t>
+          <t>随车吊租赁</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1989,7 +2051,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2002,26 +2064,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L2_lease_general</t>
+          <t>L2_labor_site</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>租赁费</t>
+          <t>工程劳工</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2034,62 +2096,58 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L2_mgmt_bank_fee</t>
+          <t>L2_lease_form</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>银行手续费</t>
+          <t>钢膜租赁</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>手续费;电汇费;转账手续费;银行转账手续费</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L2_mgmt_vehicle</t>
+          <t>L2_mat_generic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>车辆使用费</t>
+          <t>材料采购</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2098,66 +2156,66 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ETC;皮卡;租车;车辆租赁;过路费;过路过桥;车辆使用</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>车辆租赁/过路等；车辆用油单独</t>
-        </is>
-      </c>
+          <t>C型钢;H型钢;型钢;工字钢;扁钢;方钢;施工物资;材料报销;材料费;材料采购付款;材料采购费用;槽钢;物资采购;角钢;钢结构件;预埋;预埋件;预埋钢板</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L2_劳务费</t>
+          <t>L2_mgmt_clean</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>劳务费</t>
+          <t>场地清理费</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>危废;危废处理;垃圾处理;建筑垃圾;清运;垃圾清理;垃圾清理费;场地清理;渣土</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L2_物资采购</t>
+          <t>L2_eq_generator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>物资采购</t>
+          <t>发电机租赁</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2165,39 +2223,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「材料采购」</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L2_auto_缅工营地</t>
+          <t>L2_lease_general</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>缅工营地</t>
+          <t>租赁费</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2205,35 +2259,31 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>auto from learn_pool</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L2_eq_loader</t>
+          <t>L2_mgmt_bank_fee</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>铲车租赁</t>
+          <t>银行手续费</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2242,24 +2292,20 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>装载机;装载机租赁;铲车</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>含装载机</t>
-        </is>
-      </c>
+          <t>手续费;电汇费;转账手续费;银行转账手续费</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L2_mgmt_food</t>
+          <t>L2_mgmt_vehicle</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>伙食费</t>
+          <t>车辆使用费</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2273,7 +2319,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2282,34 +2328,38 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>ETC;皮卡;租车;车辆租赁;过路费;过路过桥;车辆使用</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>车辆租赁/过路等；车辆用油单独</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L2_eq_boom</t>
+          <t>L2_劳务费</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>曲臂车租赁</t>
+          <t>劳务费</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2322,66 +2372,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L2_mgmt_other</t>
+          <t>L2_物资采购</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>物资采购</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>取现;换汇</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>兜底；安保费已独立</t>
+          <t xml:space="preserve"> | 并入大类「材料采购」</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L2_eq_flatbed</t>
+          <t>L2_auto_缅工营地</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>平板车租赁</t>
+          <t>缅工营地</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2389,31 +2435,35 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>auto from learn_pool</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel</t>
+          <t>L2_eq_loader</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>燃料及动力</t>
+          <t>铲车租赁</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2422,38 +2472,38 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>燃油;加油;加油费;柴油</t>
+          <t>装载机;装载机租赁;铲车</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>无法区分机具/车辆用油时的兜底</t>
+          <t>含装载机</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L2_eq_general</t>
+          <t>L2_mgmt_food</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>机具使用费</t>
+          <t>伙食费</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2462,7 +2512,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
+          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2470,66 +2520,58 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L2_mgmt_util</t>
+          <t>L2_eq_boom</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>水电费</t>
+          <t>曲臂车租赁</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>水电;水电费合计</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L2_dep_deposit</t>
+          <t>L2_mgmt_other</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2538,56 +2580,56 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>押金;保证金退还;押金退还</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>取现;换汇</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>兜底；安保费已独立</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L2_log_customs_agent</t>
+          <t>L2_eq_flatbed</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>报关带关费</t>
+          <t>平板车租赁</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L2_mgmt_deposit</t>
+          <t>L2_mgmt_fuel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>燃料及动力</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2601,65 +2643,69 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>押金;保证金退还</t>
+          <t>燃油;加油;加油费;柴油</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>无法区分机具/车辆用油时的兜底</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L2_mgmt_park</t>
+          <t>L2_eq_general</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>园区管理费</t>
+          <t>机具使用费</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit</t>
+          <t>L2_mgmt_util</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>证件许可</t>
+          <t>水电费</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2673,7 +2719,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2682,38 +2728,38 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
+          <t>水电;水电费合计</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>工作签/施工许可类证件；商务签证归签证费用</t>
+          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2_mgmt_rent</t>
+          <t>L2_dep_deposit</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>房租物业费</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2722,7 +2768,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
+          <t>押金;保证金退还;押金退还</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2730,88 +2776,88 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L2_mgmt_flyvisa</t>
+          <t>L2_log_customs_agent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>飞签</t>
+          <t>报关带关费</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「差旅费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L2_mat_plate</t>
+          <t>L2_mgmt_deposit</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>钢板</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+          <t>押金;保证金退还</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>钢板费用，不归钢筋</t>
+          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L2_mgmt_water</t>
+          <t>L2_mgmt_park</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>饮用水付款</t>
+          <t>园区管理费</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2825,29 +2871,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「水电费」</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2_mgmt_workvisa</t>
+          <t>L2_mgmt_permit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>工作签</t>
+          <t>证件许可</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2861,29 +2903,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+          <t>工作签/施工许可类证件；商务签证归签证费用</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L2_mgmt_admin</t>
+          <t>L2_mgmt_rent</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>行政用品</t>
+          <t>房租物业费</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2897,29 +2943,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「办公费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L2_mgmt_ceremony</t>
+          <t>L2_mgmt_flyvisa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>奠基仪式费用</t>
+          <t>飞签</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2933,47 +2979,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
+          <t xml:space="preserve"> | 并入大类「差旅费」</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L2_mgmt_stamp</t>
+          <t>L2_mat_plate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>印花税</t>
+          <t>钢板</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2982,96 +3024,96 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>印花税</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>钢板费用，不归钢筋</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L2_dep_bid</t>
+          <t>L2_mgmt_water</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>饮用水付款</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>投标保证金;投标保证</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「水电费」</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L2_mat_brick</t>
+          <t>L2_mgmt_workvisa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>砖及砌块</t>
+          <t>工作签</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>数据优化</t>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L2_mgmt_agency</t>
+          <t>L2_mgmt_admin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>中介费</t>
+          <t>行政用品</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3085,25 +3127,29 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「办公费」</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa_fee</t>
+          <t>L2_mgmt_ceremony</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>签证费用</t>
+          <t>奠基仪式费用</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3117,7 +3163,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3126,38 +3172,38 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
+          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>出入境签证；工作签归证件许可</t>
+          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L2_mat_cement</t>
+          <t>L2_mgmt_stamp</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>水泥及砂浆</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_tax</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>7_税金</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3166,7 +3212,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3174,62 +3220,62 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L2_mgmt_cash</t>
+          <t>L2_dep_bid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>取现</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>投标保证金;投标保证</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L2_mgmt_work_visa</t>
+          <t>L2_mat_brick</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>工作签证费用</t>
+          <t>砖及砌块</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3238,60 +3284,56 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
+          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>工作签证相关；与商务签证、证件许可区分</t>
+          <t>数据优化</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L2_mat_sand</t>
+          <t>L2_mgmt_agency</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>砂</t>
+          <t>中介费</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2_mgmt_fx</t>
+          <t>L2_mgmt_visa_fee</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>换汇</t>
+          <t>签证费用</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3305,29 +3347,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t>出入境签证；工作签归证件许可</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2_mat_formwork</t>
+          <t>L2_mat_cement</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>模板木方</t>
+          <t>水泥及砂浆</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3341,7 +3387,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3350,7 +3396,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>木方;木模板;模板;胶合板</t>
+          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3358,12 +3404,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa</t>
+          <t>L2_mgmt_cash</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>签证费</t>
+          <t>取现</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3377,7 +3423,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3387,33 +3433,33 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2_mat_admix</t>
+          <t>L2_mgmt_work_visa</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>外加剂</t>
+          <t>工作签证费用</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3422,34 +3468,38 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>减水剂;外加剂;苏博特</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>工作签证相关；与商务签证、证件许可区分</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2_mgmt_test</t>
+          <t>L2_mat_sand</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>检验试验费</t>
+          <t>砂</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3458,168 +3508,164 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>替换/细化原检验试验</t>
-        </is>
-      </c>
+          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2_mat_slag</t>
+          <t>L2_mgmt_fx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>炉渣灰渣</t>
+          <t>换汇</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>炉渣;炉渣款;粉煤灰</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2_mgmt_toll</t>
+          <t>L2_mat_formwork</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>模板木方</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>木方;木模板;模板;胶合板</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2_mat_hardware</t>
+          <t>L2_mgmt_visa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>五金辅材</t>
+          <t>签证费</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2_mgmt_perf_bond</t>
+          <t>L2_mat_admix</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>外加剂</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>减水剂;外加剂;苏博特</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel2</t>
+          <t>L2_mgmt_test</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>燃料动力</t>
+          <t>检验试验费</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3633,43 +3679,47 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>停用：合并到燃料及动力</t>
+          <t>替换/细化原检验试验</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2_mgmt_insurance</t>
+          <t>L2_mat_slag</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>保险费</t>
+          <t>炉渣灰渣</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3678,7 +3728,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>保费;保险;工程保险;车辆保险</t>
+          <t>炉渣;炉渣款;粉煤灰</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3686,12 +3736,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2_mgmt_design</t>
+          <t>L2_mgmt_toll</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>图纸设计费</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3705,65 +3755,65 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel3</t>
+          <t>L2_mat_hardware</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>五金辅材</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>停用：合并到燃料及动力</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2_mgmt_ppe</t>
+          <t>L2_mgmt_perf_bond</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>劳保用品</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3777,65 +3827,65 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2_dep_perf</t>
+          <t>L2_mgmt_fuel2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>燃料动力</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>履约保证金;履约保证</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>停用：合并到燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L2_mgmt_gas</t>
+          <t>L2_mgmt_insurance</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>燃气煤气费</t>
+          <t>保险费</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3849,7 +3899,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3858,24 +3908,20 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>食堂/宿舍燃气；加油归燃料及动力</t>
-        </is>
-      </c>
+          <t>保费;保险;工程保险;车辆保险</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L2_mgmt_water_fee</t>
+          <t>L2_mgmt_design</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>水费</t>
+          <t>图纸设计费</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3889,7 +3935,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3898,24 +3944,20 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>施工/园区/工业用水；不含桶装饮用水</t>
-        </is>
-      </c>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L2_mgmt_elec_fee</t>
+          <t>L2_mgmt_fuel3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>电费</t>
+          <t>燃料</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3929,33 +3971,29 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>施工/临时用电；不含燃料发电</t>
+          <t>停用：合并到燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L2_mgmt_reimburse</t>
+          <t>L2_mgmt_ppe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>费用报销</t>
+          <t>劳保用品</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3969,7 +4007,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3978,7 +4016,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>报销;日常费用;郝阳报销</t>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3986,26 +4024,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L2_mgmt_drink_water</t>
+          <t>L2_dep_perf</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>现场饮用水</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4014,24 +4052,20 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>现场/办公室饮用桶装水等</t>
-        </is>
-      </c>
+          <t>履约保证金;履约保证</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_gas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>燃气煤气费</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4045,7 +4079,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4054,20 +4088,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>劳工部检查;施工许可;签字费</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>食堂/宿舍燃气；加油归燃料及动力</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_mgmt_water_fee</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>水费</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4081,7 +4119,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4090,78 +4128,74 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
+          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
+          <t>施工/园区/工业用水；不含桶装饮用水</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L2_mgmt_medical</t>
+          <t>L2_auto_押金（及费用）</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>医务费用</t>
+          <t>押金（及费用）</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>各项医务、体检、医疗费用</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_mgmt_elec_fee</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>电费</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4170,20 +4204,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>施工/临时用电；不含燃料发电</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_equip</t>
+          <t>L2_mgmt_reimburse</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>机具发电用油</t>
+          <t>费用报销</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4197,7 +4235,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4206,64 +4244,56 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>施工机具、发电机用柴油等</t>
-        </is>
-      </c>
+          <t>报销;日常费用;郝阳报销</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_vehicle</t>
+          <t>L2_auto_投标保证金（退回）</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>车辆用油</t>
+          <t>投标保证金（退回）</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>交通车辆用油</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L2_mgmt_airfare</t>
+          <t>L2_mgmt_drink_water</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>机票费</t>
+          <t>现场饮用水</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4277,7 +4307,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4286,20 +4316,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>机票;机票款;航空票;机票费用</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>现场/办公室饮用桶装水等</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L2_mgmt_transit</t>
+          <t>L2_mgmt_permit_sign</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>交通费</t>
+          <t>施工许可签字费</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4313,7 +4347,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4322,24 +4356,20 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>市内/城际交通，不含车辆租赁与过路</t>
-        </is>
-      </c>
+          <t>劳工部检查;施工许可;签字费</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel_allow</t>
+          <t>L2_mgmt_police</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>出差补助</t>
+          <t>治安管理费</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4353,7 +4383,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4362,20 +4392,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L2_mgmt_security_fee</t>
+          <t>L2_mgmt_medical</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>安保费</t>
+          <t>医务费用</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4389,43 +4423,47 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
+          <t>各项医务、体检、医疗费用</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L2_mat_floor</t>
+          <t>L2_eq_repair</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>地坪硬化</t>
+          <t>机具维修</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4434,7 +4472,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4442,12 +4480,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel</t>
+          <t>L2_mgmt_fuel_equip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>差旅费</t>
+          <t>机具发电用油</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4461,7 +4499,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4470,38 +4508,38 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>差旅;差旅费;酒店;住宿;宾馆</t>
+          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>差旅综合；机票/交通/补助请用细分科目</t>
+          <t>施工机具、发电机用柴油等</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L2_mat_gate</t>
+          <t>L2_mgmt_fuel_vehicle</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>门楼</t>
+          <t>车辆用油</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4510,34 +4548,38 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>大门;门楼施工;门头</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>交通车辆用油</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L2_mgmt_tax</t>
+          <t>L2_mgmt_airfare</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>税款</t>
+          <t>机票费</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4546,60 +4588,60 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
+          <t>机票;机票款;航空票;机票费用</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L2_auto_混凝土及泵车</t>
+          <t>L2_mgmt_transit</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>混凝土及泵车</t>
+          <t>交通费</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>auto from learn_pool</t>
+          <t>市内/城际交通，不含车辆租赁与过路</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L2_mgmt_bid_bond</t>
+          <t>L2_mgmt_travel_allow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>出差补助</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4613,33 +4655,29 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>履约保证金</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
-        </is>
-      </c>
+          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>L2_mat_temp_build</t>
+          <t>L2_mgmt_security_fee</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>现场临建用房</t>
+          <t>安保费</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4653,47 +4691,43 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>L2_mat_temp_fence</t>
+          <t>L2_mat_floor</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>现场临时围墙</t>
+          <t>地坪硬化</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4702,53 +4736,321 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>现场临时围墙/围挡；归属 6_管理费</t>
-        </is>
-      </c>
+          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>L2_mgmt_travel</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>80</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>差旅;差旅费;酒店;住宿;宾馆</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>差旅综合；机票/交通/补助请用细分科目</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L2_mat_gate</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>门楼</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>81</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>大门;门楼施工;门头</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L2_mgmt_tax</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>税款</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>L1_tax</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>7_税金</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>81</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L2_auto_混凝土及泵车</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>混凝土及泵车</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>82</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>auto from learn_pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L2_mgmt_bid_bond</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>投标保证金</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>82</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>履约保证金</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_build</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>现场临建用房</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>90</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_fence</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>现场临时围墙</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>91</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>现场临时围墙/围挡；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>L2_lease_container</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>集装箱租赁</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>L1_mgmt</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>6_管理费</t>
         </is>
       </c>
-      <c r="E108" t="n">
+      <c r="E115" t="n">
         <v>92</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
         <is>
           <t>集装箱租赁（非集装箱房临建）；归属 6_管理费</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H108"/>
+  <autoFilter ref="A1:H115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
+++ b/12_财务数据/财务付款数据/learn_classify/data/科目体系.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'一级科目'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'二级科目'!$A$1:$H$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'三级科目'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -854,8 +854,133 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L1_auto_9_备用金</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9_备用金</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>83</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L1_auto_1_工程款</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1_工程款</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L1_auto_3_收入</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3_收入</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>85</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L1_auto_9_押金</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9_押金</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>86</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L1_auto_2_搅拌站销售</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2_搅拌站销售</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>87</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -866,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1232,22 +1357,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L2_auto_废旧物资处理</t>
+          <t>L2_auto_备用金（冲）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>废旧物资处理</t>
+          <t>备用金（冲）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L1_auto_其他收款</t>
+          <t>L1_auto_9_备用金</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>其他收款</t>
+          <t>9_备用金</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1268,22 +1393,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L2_eq_tower</t>
+          <t>L2_auto_废旧物资处理</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>塔吊租赁</t>
+          <t>废旧物资处理</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_auto_其他收款</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>其他收款</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1295,27 +1420,31 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L2_exclude_transfer</t>
+          <t>L2_auto_押金退款</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>资金调拨</t>
+          <t>押金退款</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_auto_9_押金</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>9_押金</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1329,29 +1458,29 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L2_labor_salary</t>
+          <t>L2_auto_泵车</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>工资薪金</t>
+          <t>泵车</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_auto_2_搅拌站销售</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>2_搅拌站销售</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1363,27 +1492,31 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L2_lease_plate</t>
+          <t>L2_auto_银行利息</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>钢板租赁</t>
+          <t>银行利息</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_auto_3_收入</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>3_收入</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1394,32 +1527,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>TCB钢板;钢板租赁</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L2_log_customs</t>
+          <t>L2_auto_项目收款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>关税物流费</t>
+          <t>项目收款</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_auto_1_工程款</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>1_工程款</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1430,32 +1563,32 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>关税;物流费;关税物流;进口税</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L2_mat_steel</t>
+          <t>L2_eq_tower</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>钢筋</t>
+          <t>塔吊租赁</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1466,32 +1599,28 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>圆钢;盘圆;线材;螺纹钢;钢筋;钢绞线</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L2_mgmt_safety</t>
+          <t>L2_exclude_transfer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>安全费用</t>
+          <t>资金调拨</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1499,35 +1628,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 已并入治安管理费；体检/医疗→医务费用</t>
+          <t>seed extra</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L2_sub_loan</t>
+          <t>L2_labor_salary</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>分包借款</t>
+          <t>工资薪金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L1_sub</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0_分包</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1544,170 +1673,170 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L2_auto_地勘收款</t>
+          <t>L2_lease_plate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>地勘收款</t>
+          <t>钢板租赁</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1_auto_其他收款</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>其他收款</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>auto from ledger_book</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TCB钢板;钢板租赁</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L2_auto_进度款</t>
+          <t>L2_log_customs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>进度款</t>
+          <t>关税物流费</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L1_auto_工程款</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>工程款</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>auto from ledger_book</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>关税;物流费;关税物流;进口税</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L2_eq_excavator</t>
+          <t>L2_mat_steel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>挖机租赁</t>
+          <t>钢筋</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>圆钢;盘圆;线材;螺纹钢;钢筋;钢绞线</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L2_exclude_agent_pay</t>
+          <t>L2_mgmt_safety</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>代付款</t>
+          <t>安全费用</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L1_sub</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0_分包</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>代付/代垫款；归属 0_分包（计入成本）</t>
+          <t xml:space="preserve"> | 已并入治安管理费；体检/医疗→医务费用</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L2_exclude_other</t>
+          <t>L2_sub_loan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>分包借款</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_sub</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>0_分包</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1715,31 +1844,27 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>seed extra</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L2_labor_mm</t>
+          <t>L2_auto_分包管理费</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>缅工</t>
+          <t>分包管理费</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_auto_1_工程款</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>1_工程款</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1751,27 +1876,31 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L2_lease_pipe</t>
+          <t>L2_auto_地勘收款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>钢管租赁</t>
+          <t>地勘收款</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_auto_其他收款</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>其他收款</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1783,27 +1912,31 @@
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L2_mat_pile</t>
+          <t>L2_auto_无摘要</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>桩</t>
+          <t>无摘要</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_auto_3_收入</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_收入</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1815,27 +1948,31 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L2_mgmt_office</t>
+          <t>L2_auto_进度款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>办公费</t>
+          <t>进度款</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_auto_工程款</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1846,40 +1983,36 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>中央空调安装;分体空调;办公空调;办公费;安装空调;空调;空调安装;空调移机;空调维修;空调费;行政办公</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L2_auto_工程款</t>
+          <t>L2_eq_excavator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>工程款</t>
+          <t>挖机租赁</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L1_auto_工程款</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>工程款</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1887,67 +2020,71 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>auto from ledger_book</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L2_eq_crane</t>
+          <t>L2_exclude_agent_pay</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>吊车租赁</t>
+          <t>代付款</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_sub</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>0_分包</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>代付;代付款;代支付;代垫;代垫款;代为付款</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>代付/代垫款；归属 0_分包（计入成本）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L2_labor_local</t>
+          <t>L2_exclude_other</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>属地员工</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1955,103 +2092,99 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L2_mat_gravel</t>
+          <t>L2_labor_mm</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>碎石</t>
+          <t>缅工</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>寸石;石子;碎石料;级配砂石</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L2_mgmt_petty</t>
+          <t>L2_lease_pipe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>备用金</t>
+          <t>钢管租赁</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>L1_exclude</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>不计入成本</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>借支;备用金;预支</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L2_eq_truckcrane</t>
+          <t>L2_mat_pile</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>随车吊租赁</t>
+          <t>桩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2064,58 +2197,66 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L2_labor_site</t>
+          <t>L2_mgmt_office</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>工程劳工</t>
+          <t>办公费</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>中央空调安装;分体空调;办公空调;办公费;安装空调;空调;空调安装;空调移机;空调维修;空调费;行政办公</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>管理费下二级；其下有三级：网络/邮寄/办公物品/其他办公</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L2_lease_form</t>
+          <t>L2_auto_工程款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>钢膜租赁</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_auto_工程款</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>工程款</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2123,229 +2264,225 @@
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L2_mat_generic</t>
+          <t>L2_eq_crane</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>材料采购</t>
+          <t>吊车租赁</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>C型钢;H型钢;型钢;工字钢;扁钢;方钢;施工物资;材料报销;材料费;材料采购付款;材料采购费用;槽钢;物资采购;角钢;钢结构件;预埋;预埋件;预埋钢板</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L2_mgmt_clean</t>
+          <t>L2_labor_local</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>场地清理费</t>
+          <t>属地员工</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>危废;危废处理;垃圾处理;建筑垃圾;清运;垃圾清理;垃圾清理费;场地清理;渣土</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L2_eq_generator</t>
+          <t>L2_mat_gravel</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>发电机租赁</t>
+          <t>碎石</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>寸石;石子;碎石料;级配砂石</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L2_lease_general</t>
+          <t>L2_mgmt_petty</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>租赁费</t>
+          <t>备用金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L1_lease</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4_材料租赁</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>借支;备用金;预支</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L2_mgmt_bank_fee</t>
+          <t>L2_auto_业主多付款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>银行手续费</t>
+          <t>业主多付款</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_exclude</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>不计入成本</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>手续费;电汇费;转账手续费;银行转账手续费</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L2_mgmt_vehicle</t>
+          <t>L2_eq_truckcrane</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>车辆使用费</t>
+          <t>随车吊租赁</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ETC;皮卡;租车;车辆租赁;过路费;过路过桥;车辆使用</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>车辆租赁/过路等；车辆用油单独</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L2_劳务费</t>
+          <t>L2_labor_site</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>劳务费</t>
+          <t>工程劳工</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2359,7 +2496,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2372,98 +2509,94 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L2_物资采购</t>
+          <t>L2_lease_form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>物资采购</t>
+          <t>钢膜租赁</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「材料采购」</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L2_auto_缅工营地</t>
+          <t>L2_mat_generic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>缅工营地</t>
+          <t>材料采购</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L1_labor</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1_人工费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>auto from learn_pool</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C型钢;H型钢;型钢;工字钢;扁钢;方钢;施工物资;材料报销;材料费;材料采购付款;材料采购费用;槽钢;物资采购;角钢;钢结构件;预埋;预埋件;预埋钢板</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L2_eq_loader</t>
+          <t>L2_mgmt_clean</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>铲车租赁</t>
+          <t>场地清理费</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2472,74 +2605,66 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>装载机;装载机租赁;铲车</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>含装载机</t>
-        </is>
-      </c>
+          <t>危废;危废处理;垃圾处理;建筑垃圾;清运;垃圾清理;垃圾清理费;场地清理;渣土</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L2_mgmt_food</t>
+          <t>L2_eq_generator</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>伙食费</t>
+          <t>发电机租赁</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L2_eq_boom</t>
+          <t>L2_lease_general</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>曲臂车租赁</t>
+          <t>租赁费</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_lease</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>4_材料租赁</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2552,12 +2677,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L2_mgmt_other</t>
+          <t>L2_mgmt_bank_fee</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行手续费</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2571,7 +2696,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2580,186 +2705,178 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>取现;换汇</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>兜底；安保费已独立</t>
-        </is>
-      </c>
+          <t>手续费;电汇费;转账手续费;银行转账手续费</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L2_eq_flatbed</t>
+          <t>L2_mgmt_vehicle</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>平板车租赁</t>
+          <t>车辆使用费</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ETC;皮卡;租车;车辆租赁;过路费;过路过桥;车辆使用</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>车辆租赁/过路等；车辆用油单独</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel</t>
+          <t>L2_劳务费</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>燃料及动力</t>
+          <t>劳务费</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>燃油;加油;加油费;柴油</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>无法区分机具/车辆用油时的兜底</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L2_eq_general</t>
+          <t>L2_物资采购</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>机具使用费</t>
+          <t>物资采购</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「材料采购」</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L2_mgmt_util</t>
+          <t>L2_auto_缅工营地</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>水电费</t>
+          <t>缅工营地</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>水电;水电费合计</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
+          <t>auto from learn_pool</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2_dep_deposit</t>
+          <t>L2_eq_loader</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>铲车租赁</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2768,34 +2885,38 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>押金;保证金退还;押金退还</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>装载机;装载机租赁;铲车</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>含装载机</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L2_log_customs_agent</t>
+          <t>L2_mgmt_food</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>报关带关费</t>
+          <t>伙食费</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L1_logistics</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5_关税物流</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2804,7 +2925,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
+          <t>伙食;食堂;餐费;误餐;盒饭;工作餐</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2812,66 +2933,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L2_mgmt_deposit</t>
+          <t>L2_auto_个税</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>押金</t>
+          <t>个税</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>押金;保证金退还</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L2_mgmt_park</t>
+          <t>L2_eq_boom</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>园区管理费</t>
+          <t>曲臂车租赁</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2884,12 +3001,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit</t>
+          <t>L2_mgmt_other</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>证件许可</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2903,7 +3020,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2912,110 +3029,106 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
+          <t>取现;换汇</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>工作签/施工许可类证件；商务签证归签证费用</t>
+          <t>兜底；安保费已独立</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L2_mgmt_rent</t>
+          <t>L2_auto_正式工</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>房租物业费</t>
+          <t>正式工</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L2_mgmt_flyvisa</t>
+          <t>L2_eq_flatbed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>飞签</t>
+          <t>平板车租赁</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「差旅费」</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L2_mat_plate</t>
+          <t>L2_mgmt_fuel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>钢板</t>
+          <t>燃料及动力</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3024,96 +3137,96 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+          <t>燃油;加油;加油费;柴油</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>钢板费用，不归钢筋</t>
+          <t>无法区分机具/车辆用油时的兜底</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L2_mgmt_water</t>
+          <t>L2_auto_劳务工资</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>饮用水付款</t>
+          <t>劳务工资</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_labor</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>1_人工费</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「水电费」</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L2_mgmt_workvisa</t>
+          <t>L2_eq_general</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>工作签</t>
+          <t>机具使用费</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>临租;机具款;机械租赁;机械租赁费;设备租赁</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L2_mgmt_admin</t>
+          <t>L2_mgmt_util</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>行政用品</t>
+          <t>水电费</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3127,43 +3240,47 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>水电;水电费合计</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「办公费」</t>
+          <t>无法区分水/电时的兜底；优先用水费/电费/现场饮用水</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L2_mgmt_ceremony</t>
+          <t>L2_dep_deposit</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>奠基仪式费用</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3172,38 +3289,34 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
-        </is>
-      </c>
+          <t>押金;保证金退还;押金退还</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L2_mgmt_stamp</t>
+          <t>L2_log_customs_agent</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>印花税</t>
+          <t>报关带关费</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_logistics</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>5_关税物流</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3212,7 +3325,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>印花税</t>
+          <t>保关费;带关费;带关费用;报关;清关;报关费;带关</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3220,88 +3333,84 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L2_dep_bid</t>
+          <t>L2_mgmt_deposit</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>押金</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>投标保证金;投标保证</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>押金;保证金退还</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L2_mat_brick</t>
+          <t>L2_mgmt_park</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>砖及砌块</t>
+          <t>园区管理费</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>数据优化</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L2_mgmt_agency</t>
+          <t>L2_mgmt_permit</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>中介费</t>
+          <t>证件许可</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3315,25 +3424,33 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>BOI;DBD;劳工证;许可证;证件;证件许可</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>工作签/施工许可类证件；商务签证归签证费用</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa_fee</t>
+          <t>L2_mgmt_rent</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>签证费用</t>
+          <t>房租物业费</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3347,7 +3464,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3356,96 +3473,96 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>出入境签证；工作签归证件许可</t>
-        </is>
-      </c>
+          <t>宿舍;宿舍租金;房租;营地;物业费;房租物业;宿舍费</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2_mat_cement</t>
+          <t>L2_mgmt_flyvisa</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>水泥及砂浆</t>
+          <t>飞签</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「差旅费」</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2_mgmt_cash</t>
+          <t>L2_mat_plate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>取现</t>
+          <t>钢板</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>钢板费用;钢板费;钢板采购;钢板款;钢板材料</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t>钢板费用，不归钢筋</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2_mgmt_work_visa</t>
+          <t>L2_mgmt_water</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>工作签证费用</t>
+          <t>饮用水付款</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3459,69 +3576,65 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>工作签证相关；与商务签证、证件许可区分</t>
+          <t xml:space="preserve"> | 并入大类「水电费」</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2_mat_sand</t>
+          <t>L2_mgmt_workvisa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>砂</t>
+          <t>工作签</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2_mgmt_fx</t>
+          <t>L2_mgmt_admin</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>换汇</t>
+          <t>行政用品</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3535,7 +3648,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3545,33 +3658,33 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「其他」</t>
+          <t xml:space="preserve"> | 并入大类「办公费」</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2_mat_formwork</t>
+          <t>L2_mgmt_ceremony</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>模板木方</t>
+          <t>奠基仪式费用</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3580,70 +3693,74 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>木方;木模板;模板;胶合板</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>仪式花篮;奠基;奠基仪式;奠基仪式费;奠基石;开工仪式;开工仪式费;开工奠基;开工奠基仪式</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>开工/奠基仪式相关费用（餐费、用车除外）</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2_mgmt_visa</t>
+          <t>L2_mgmt_stamp</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>签证费</t>
+          <t>印花税</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_tax</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>7_税金</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | 并入大类「证件许可」</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>印花税</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2_mat_admix</t>
+          <t>L2_dep_bid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>外加剂</t>
+          <t>投标保证金</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3652,7 +3769,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>减水剂;外加剂;苏博特</t>
+          <t>投标保证金;投标保证</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -3660,26 +3777,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2_mgmt_test</t>
+          <t>L2_mat_brick</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>检验试验费</t>
+          <t>砖及砌块</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3688,60 +3805,56 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
+          <t>加气块;实心砖;水泥砖;砌块;空心砖</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>替换/细化原检验试验</t>
+          <t>数据优化</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2_mat_slag</t>
+          <t>L2_mgmt_agency</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>炉渣灰渣</t>
+          <t>中介费</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>炉渣;炉渣款;粉煤灰</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2_mgmt_toll</t>
+          <t>L2_mgmt_visa_fee</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>签证费用</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3755,29 +3868,33 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DTV;商务签;回头签;年签;签证;签证费;签证费用;老挝签;转签;飞签</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
+          <t>出入境签证；工作签归证件许可</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2_mat_hardware</t>
+          <t>L2_mat_cement</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>五金辅材</t>
+          <t>水泥及砂浆</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3791,7 +3908,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3800,7 +3917,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+          <t>抹灰砂浆;水泥;砂浆;砌筑砂浆;预拌砂浆</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3808,12 +3925,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2_mgmt_perf_bond</t>
+          <t>L2_mgmt_cash</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>取现</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3827,7 +3944,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3837,19 +3954,19 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel2</t>
+          <t>L2_mgmt_work_visa</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>燃料动力</t>
+          <t>工作签证费用</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3863,43 +3980,47 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>临时工作签;临时工作证;临时工作证费用;办理工作证;工作签;工作签证;工作签证费用;工作签费;工作签费用;工作证;工作证费;工作证费用;工签;工签费;落地签;落地签证;落地签证费;落地签证费用;落地签费用</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>停用：合并到燃料及动力</t>
+          <t>工作签证相关；与商务签证、证件许可区分</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L2_mgmt_insurance</t>
+          <t>L2_mat_sand</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>保险费</t>
+          <t>砂</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3908,7 +4029,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>保费;保险;工程保险;车辆保险</t>
+          <t>中砂;机制砂;沙子;河沙;粗砂;黄沙</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -3916,12 +4037,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L2_mgmt_design</t>
+          <t>L2_mgmt_fx</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>图纸设计费</t>
+          <t>换汇</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3935,65 +4056,65 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「其他」</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel3</t>
+          <t>L2_mat_formwork</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>燃料</t>
+          <t>模板木方</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>停用：合并到燃料及动力</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>木方;木模板;模板;胶合板</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L2_mgmt_ppe</t>
+          <t>L2_mgmt_visa</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>劳保用品</t>
+          <t>签证费</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4007,43 +4128,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「证件许可」</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L2_dep_perf</t>
+          <t>L2_mat_admix</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>外加剂</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4052,7 +4173,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>履约保证金;履约保证</t>
+          <t>减水剂;外加剂;苏博特</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4060,12 +4181,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2_mgmt_gas</t>
+          <t>L2_mgmt_test</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>燃气煤气费</t>
+          <t>检验试验费</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4079,7 +4200,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4088,38 +4209,38 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
+          <t>一线检测;三线检测;低应变;大小应变;桩检;检测费;检验试验;试验费;高应变</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>食堂/宿舍燃气；加油归燃料及动力</t>
+          <t>替换/细化原检验试验</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2_mgmt_water_fee</t>
+          <t>L2_mat_slag</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>水费</t>
+          <t>炉渣灰渣</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4128,74 +4249,70 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>施工/园区/工业用水；不含桶装饮用水</t>
-        </is>
-      </c>
+          <t>炉渣;炉渣款;粉煤灰</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L2_auto_押金（及费用）</t>
+          <t>L2_mgmt_toll</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>押金（及费用）</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>auto from ledger_book</t>
+          <t xml:space="preserve"> | 并入大类「车辆使用费」</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L2_mgmt_elec_fee</t>
+          <t>L2_mat_hardware</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>电费</t>
+          <t>五金辅材</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_mat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>2_材料采购</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4204,24 +4321,20 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>施工/临时用电；不含燃料发电</t>
-        </is>
-      </c>
+          <t>DOHOME;HARDWAREHOUSE;hardware;五金;辅材;零星材料</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>L2_mgmt_reimburse</t>
+          <t>L2_mgmt_perf_bond</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>费用报销</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4235,65 +4348,65 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>报销;日常费用;郝阳报销</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 并入大类「投标保证金」 | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>L2_auto_投标保证金（退回）</t>
+          <t>L2_mgmt_fuel2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>投标保证金（退回）</t>
+          <t>燃料动力</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>L1_deposit</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>8_押金保证金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>auto from ledger_book</t>
+          <t>停用：合并到燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L2_mgmt_drink_water</t>
+          <t>L2_mgmt_insurance</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>现场饮用水</t>
+          <t>保险费</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4307,7 +4420,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4316,24 +4429,20 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>现场/办公室饮用桶装水等</t>
-        </is>
-      </c>
+          <t>保费;保险;工程保险;车辆保险</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L2_mgmt_permit_sign</t>
+          <t>L2_mgmt_design</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>施工许可签字费</t>
+          <t>图纸设计费</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4347,7 +4456,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4356,7 +4465,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>劳工部检查;施工许可;签字费</t>
+          <t>图纸;图纸签字;工程师签字;设计费;转图</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4364,12 +4473,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L2_mgmt_police</t>
+          <t>L2_mgmt_fuel3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>治安管理费</t>
+          <t>燃料</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4383,33 +4492,29 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
+          <t>停用：合并到燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L2_mgmt_medical</t>
+          <t>L2_mgmt_ppe</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>医务费用</t>
+          <t>劳保用品</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4423,7 +4528,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4432,38 +4537,34 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>各项医务、体检、医疗费用</t>
-        </is>
-      </c>
+          <t>劳保;反光背心;安全带;安全帽;工作服;手套</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L2_eq_repair</t>
+          <t>L2_dep_perf</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>机具维修</t>
+          <t>履约保证金</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L1_equip</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3_机具费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4472,7 +4573,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+          <t>履约保证金;履约保证</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4480,12 +4581,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_equip</t>
+          <t>L2_mgmt_gas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>机具发电用油</t>
+          <t>燃气煤气费</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4499,7 +4600,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4508,24 +4609,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
+          <t>厨房煤气;液化气;煤气;煤气费用;燃气;食堂煤气</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>施工机具、发电机用柴油等</t>
+          <t>食堂/宿舍燃气；加油归燃料及动力</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L2_mgmt_fuel_vehicle</t>
+          <t>L2_mgmt_water_fee</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>车辆用油</t>
+          <t>水费</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4539,7 +4640,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4548,60 +4649,60 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
+          <t>园区水费;工业用水;施工用水;现场用水;生活用水;自来水</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>交通车辆用油</t>
+          <t>施工/园区/工业用水；不含桶装饮用水</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L2_mgmt_airfare</t>
+          <t>L2_auto_押金（及费用）</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>机票费</t>
+          <t>押金（及费用）</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>机票;机票款;航空票;机票费用</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L2_mgmt_transit</t>
+          <t>L2_mgmt_elec_fee</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>交通费</t>
+          <t>电费</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4615,7 +4716,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4624,24 +4725,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
+          <t>施工用电;临时用电;工业用电;现场用电;营地电力;用电安装</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>市内/城际交通，不含车辆租赁与过路</t>
+          <t>施工/临时用电；不含燃料发电</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel_allow</t>
+          <t>L2_mgmt_reimburse</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>出差补助</t>
+          <t>费用报销</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4655,7 +4756,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4664,7 +4765,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
+          <t>报销;日常费用;郝阳报销</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -4672,62 +4773,62 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>L2_mgmt_security_fee</t>
+          <t>L2_auto_投标保证金（退回）</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>安保费</t>
+          <t>投标保证金（退回）</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_deposit</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>8_押金保证金</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>L2_mat_floor</t>
+          <t>L2_mgmt_drink_water</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>地坪硬化</t>
+          <t>现场饮用水</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4736,20 +4837,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>桶装水;饮用水;矿泉水;瓶装水;饮用水付款;现场桶装水;办公室桶装水</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>现场/办公室饮用桶装水等</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>L2_mgmt_travel</t>
+          <t>L2_mgmt_permit_sign</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>差旅费</t>
+          <t>施工许可签字费</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4763,7 +4868,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4772,38 +4877,34 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>差旅;差旅费;酒店;住宿;宾馆</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>差旅综合；机票/交通/补助请用细分科目</t>
-        </is>
-      </c>
+          <t>劳工部检查;施工许可;签字费</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>L2_mat_gate</t>
+          <t>L2_mgmt_police</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>门楼</t>
+          <t>治安管理费</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4812,34 +4913,38 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>大门;门楼施工;门头</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>保安费;安保;安保公司;安保费;安保费用;安全文明;安全费;安全费用;治安;治安管理;治安管理付款;治安管理费;治安费;门卫费;门岗</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>治安/安保/安全相关统一归入；医务体检归医务费用</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>L2_mgmt_tax</t>
+          <t>L2_mgmt_medical</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>税款</t>
+          <t>医务费用</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>L1_tax</t>
+          <t>L1_mgmt</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7_税金</t>
+          <t>6_管理费</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4848,60 +4953,60 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
+          <t>医务;医务费;医务费用;体检;体检费;医疗;医疗费;药品;药费;就医;门诊;住院;医务体检;健康体检</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>seed extra</t>
+          <t>各项医务、体检、医疗费用</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>L2_auto_混凝土及泵车</t>
+          <t>L2_eq_repair</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>混凝土及泵车</t>
+          <t>机具维修</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>L1_mat</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2_材料采购</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>auto from learn_pool</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>机具维修;机械维修;补胎;设备维修;车辆维修</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>L2_mgmt_bid_bond</t>
+          <t>L2_mgmt_fuel_equip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>投标保证金</t>
+          <t>机具发电用油</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4915,73 +5020,69 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>履约保证金</t>
+          <t>机具用油;发电用油;发电机用油;机械用油;施工用油;挖机加油;吊车加油;设备加油</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+          <t>施工机具、发电机用柴油等</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>L2_mat_temp_build</t>
+          <t>L2_auto_固定资产</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>现场临建用房</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>L1_mgmt</t>
+          <t>L1_equip</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6_管理费</t>
+          <t>3_机具费</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+          <t>auto from ledger_book</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>L2_mat_temp_fence</t>
+          <t>L2_mgmt_fuel_vehicle</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>现场临时围墙</t>
+          <t>车辆用油</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4995,7 +5096,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5004,53 +5105,581 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+          <t>车辆加油;汽车加油;皮卡加油;95汽油;92汽油;汽油;交通用油</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>现场临时围墙/围挡；归属 6_管理费</t>
+          <t>交通车辆用油</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>L2_mgmt_airfare</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>机票费</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>50</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>机票;机票款;航空票;机票费用</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L2_mgmt_transit</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>交通费</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>51</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>打车;出租车;网约车;地铁;公交;大巴;交通费用;车站</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>市内/城际交通，不含车辆租赁与过路</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L2_mgmt_travel_allow</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>出差补助</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>52</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>出差补贴;差旅补助;出差津贴;驻外补助;外勤补助</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L2_mgmt_security_fee</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>安保费</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>60</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>非工资类安保服务费；保安工资在人工费 | 已并入治安管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L2_mat_floor</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>地坪硬化</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>80</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>硬化地坪;混凝土地坪;场地硬化;地坪</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>L2_mgmt_travel</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>80</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>差旅;差旅费;酒店;住宿;宾馆</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>差旅综合；机票/交通/补助请用细分科目</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L2_mat_gate</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>门楼</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>81</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>大门;门楼施工;门头</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L2_mgmt_tax</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>税款</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>L1_tax</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>7_税金</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>81</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>WHT;代扣税;增值税;税款;税金;补缴税;预扣税</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>seed extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L2_auto_混凝土及泵车</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>混凝土及泵车</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>82</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>auto from learn_pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L2_mgmt_bid_bond</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>投标保证金</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>82</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>履约保证金</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>seed extra | 已迁移到 L1_deposit，见 L2_dep_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>L2_auto_回款</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>回款</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>L1_mat</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2_材料采购</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>83</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_build</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>现场临建用房</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>90</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>临建;临时用房;活动板房;板房;临建设施;集装箱房</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>现场临建用房/活动板房等；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>L2_mat_temp_fence</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>现场临时围墙</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>91</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>临时围墙;围挡;围墙;彩钢围挡;施工围墙</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>现场临时围墙/围挡；归属 6_管理费</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>L2_lease_container</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>集装箱租赁</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>L1_mgmt</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>6_管理费</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="E128" t="n">
         <v>92</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
         <is>
           <t>集装箱租赁（非集装箱房临建）；归属 6_管理费</t>
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>L2_auto_服务费</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>服务费</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>L1_mgmt</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>6_管理费</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>93</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>auto from ledger_book</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
